--- a/src/main/resources/template/demoTemplate.xlsx
+++ b/src/main/resources/template/demoTemplate.xlsx
@@ -20,11 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">total</t>
   </si>
   <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
     <t xml:space="preserve">part1</t>
   </si>
   <si>
@@ -37,6 +40,9 @@
     <t xml:space="preserve">sum</t>
   </si>
   <si>
+    <t xml:space="preserve">{.name}</t>
+  </si>
+  <si>
     <t xml:space="preserve">{.chinese}</t>
   </si>
   <si>
@@ -47,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">{.sum}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -130,16 +139,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -266,7 +279,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -275,9 +288,10 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -289,24 +303,35 @@
       <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
+      <c r="A3" s="0" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="0" t="s">
         <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/main/resources/template/demoTemplate.xlsx
+++ b/src/main/resources/template/demoTemplate.xlsx
@@ -20,11 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">total</t>
   </si>
   <si>
+    <t xml:space="preserve">时间：{date}</t>
+  </si>
+  <si>
     <t xml:space="preserve">name</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">统计：{total}</t>
   </si>
 </sst>
 </file>
@@ -139,20 +145,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -279,8 +289,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.22"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -291,47 +304,60 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
